--- a/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\GDPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\elec\GDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF73F71-0543-43DC-85EF-555AF13B1D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC2B0FF-4EE1-4547-8D93-802C0A7902F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -523,84 +523,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -616,14 +616,14 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BE25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="27.40625" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -735,8 +735,68 @@
       <c r="AK1">
         <v>2050</v>
       </c>
+      <c r="AL1">
+        <v>2051</v>
+      </c>
+      <c r="AM1">
+        <v>2052</v>
+      </c>
+      <c r="AN1">
+        <v>2053</v>
+      </c>
+      <c r="AO1">
+        <v>2054</v>
+      </c>
+      <c r="AP1">
+        <v>2055</v>
+      </c>
+      <c r="AQ1">
+        <v>2056</v>
+      </c>
+      <c r="AR1">
+        <v>2057</v>
+      </c>
+      <c r="AS1">
+        <v>2058</v>
+      </c>
+      <c r="AT1">
+        <v>2059</v>
+      </c>
+      <c r="AU1">
+        <v>2060</v>
+      </c>
+      <c r="AV1">
+        <v>2061</v>
+      </c>
+      <c r="AW1">
+        <v>2062</v>
+      </c>
+      <c r="AX1">
+        <v>2063</v>
+      </c>
+      <c r="AY1">
+        <v>2064</v>
+      </c>
+      <c r="AZ1">
+        <v>2065</v>
+      </c>
+      <c r="BA1">
+        <v>2066</v>
+      </c>
+      <c r="BB1">
+        <v>2067</v>
+      </c>
+      <c r="BC1">
+        <v>2068</v>
+      </c>
+      <c r="BD1">
+        <v>2069</v>
+      </c>
+      <c r="BE1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -748,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:AK10" si="0">$B2</f>
+        <f t="shared" ref="D2:AL10" si="0">$B2</f>
         <v>0</v>
       </c>
       <c r="E2">
@@ -883,8 +943,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" ref="AL2:BB15" si="1">$B2</f>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <f t="shared" ref="BB2:BE15" si="2">$B2</f>
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -896,143 +1036,223 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:AK4" si="1">$B3</f>
+        <f t="shared" ref="D3:AL4" si="3">$B3</f>
         <v>0</v>
       </c>
       <c r="E3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1044,143 +1264,223 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1188,7 +1488,7 @@
         <v>0.5</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:C15" si="2">$B5</f>
+        <f t="shared" ref="C5:C15" si="4">$B5</f>
         <v>0.5</v>
       </c>
       <c r="D5">
@@ -1327,8 +1627,88 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
+      <c r="AL5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="BA5">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="BB5">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="BC5">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="BD5">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="BE5">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1336,147 +1716,227 @@
         <v>0.5</v>
       </c>
       <c r="C6">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AG6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="BA6">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="BB6">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="L6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="P6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="U6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="V6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="W6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="X6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="Y6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="Z6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AA6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AB6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AE6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AF6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AG6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AH6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AI6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AJ6">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AK6">
-        <f t="shared" si="0"/>
+      <c r="BC6">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="BD6">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="BE6">
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1484,147 +1944,227 @@
         <v>0.8</v>
       </c>
       <c r="C7">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AE7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="BA7">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="BB7">
         <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="L7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="O7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="P7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="U7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="V7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="W7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="X7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="Y7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="Z7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AA7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AB7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AE7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AF7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AG7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AH7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AI7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AJ7">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AK7">
-        <f t="shared" si="0"/>
+      <c r="BC7">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="BD7">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="BE7">
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1632,147 +2172,227 @@
         <v>0.8</v>
       </c>
       <c r="C8">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="BA8">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="BB8">
         <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="O8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="P8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="U8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="V8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="W8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="X8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="Y8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="Z8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AA8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AB8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AC8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AD8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AE8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AF8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AG8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AH8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AI8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AJ8">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AK8">
-        <f t="shared" si="0"/>
+      <c r="BC8">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="BD8">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="BE8">
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1780,147 +2400,227 @@
         <v>0.8</v>
       </c>
       <c r="C9">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AB9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AG9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AJ9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AK9">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="AL9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AN9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AO9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AP9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AQ9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AR9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AS9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AT9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AU9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AV9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AW9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AX9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AY9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AZ9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="BA9">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="BB9">
         <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="O9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="P9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="W9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="X9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="Y9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="Z9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AA9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AB9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AC9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AD9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AE9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AF9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AG9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AH9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AI9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AJ9">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="AK9">
-        <f t="shared" si="0"/>
+      <c r="BC9">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="BD9">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="BE9">
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1928,147 +2628,227 @@
         <v>0.5</v>
       </c>
       <c r="C10">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AB10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AG10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="AJ10">
+        <f t="shared" ref="D10:AL15" si="5">$B10</f>
+        <v>0.5</v>
+      </c>
+      <c r="AK10">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AL10">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AM10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AN10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AO10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AP10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AQ10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AR10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AS10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AT10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AU10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AV10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AW10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AX10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AY10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AZ10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="BA10">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="BB10">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="O10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="P10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="U10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="V10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="W10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="X10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="Y10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="Z10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AA10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AB10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AC10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AD10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AE10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AF10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AG10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AH10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AI10">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="AJ10">
-        <f t="shared" ref="D10:AK15" si="3">$B10</f>
-        <v>0.5</v>
-      </c>
-      <c r="AK10">
-        <f t="shared" si="3"/>
+      <c r="BC10">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="BD10">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="BE10">
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -2076,147 +2856,227 @@
         <v>0.8</v>
       </c>
       <c r="C11">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="AB11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="AE11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="AG11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="AH11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="AI11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="AJ11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="AK11">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="AL11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AM11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AN11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AO11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AP11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AQ11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AR11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AS11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AT11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AU11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AV11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AW11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AX11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AY11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="AZ11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="BA11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="BB11">
         <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="D11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="O11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="P11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="U11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="W11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="X11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="Y11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="Z11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="AA11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="AB11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="AC11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="AD11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="AE11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="AF11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="AG11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="AH11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="AI11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="AJ11">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
-      </c>
-      <c r="AK11">
-        <f t="shared" si="3"/>
+      <c r="BC11">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="BD11">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="BE11">
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -2224,147 +3084,227 @@
         <v>0</v>
       </c>
       <c r="C12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <f t="shared" si="3"/>
+      <c r="BC12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -2372,147 +3312,227 @@
         <v>0</v>
       </c>
       <c r="C13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <f t="shared" si="3"/>
+      <c r="BC13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -2520,147 +3540,227 @@
         <v>0</v>
       </c>
       <c r="C14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <f t="shared" si="3"/>
+      <c r="BC14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -2668,147 +3768,227 @@
         <v>0</v>
       </c>
       <c r="C15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AK15">
-        <f t="shared" si="3"/>
+      <c r="BC15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -2817,147 +3997,227 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <f t="shared" ref="C16:AK16" si="4">C12</f>
+        <f t="shared" ref="C16:AK16" si="6">C12</f>
         <v>0</v>
       </c>
       <c r="D16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AH16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AI16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AJ16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <f t="shared" ref="AL16:BA16" si="7">AL12</f>
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <f t="shared" ref="BB16:BE16" si="8">BB12</f>
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -2966,147 +4226,227 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <f t="shared" ref="C17:AK17" si="5">C12</f>
+        <f t="shared" ref="C17:AK17" si="9">C12</f>
         <v>0</v>
       </c>
       <c r="D17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AG17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AI17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AK17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <f t="shared" ref="AL17:BA17" si="10">AL12</f>
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <f t="shared" ref="BB17:BE17" si="11">BB12</f>
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -3115,147 +4455,227 @@
         <v>0.5</v>
       </c>
       <c r="C18">
-        <f t="shared" ref="C18:AK18" si="6">C10</f>
+        <f t="shared" ref="C18:AK18" si="12">C10</f>
         <v>0.5</v>
       </c>
       <c r="D18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="E18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="F18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="G18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="H18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="I18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="J18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="K18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="L18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="M18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="N18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="O18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="P18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="R18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="S18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="T18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="U18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="V18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="W18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="X18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="Y18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="Z18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="AA18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="AB18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="AC18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="AD18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="AE18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="AF18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="AG18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="AH18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="AI18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="AJ18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="AK18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="AL18">
+        <f t="shared" ref="AL18:BA18" si="13">AL10</f>
+        <v>0.5</v>
+      </c>
+      <c r="AM18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AN18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AO18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AP18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AQ18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AR18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AS18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AT18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AU18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AV18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AW18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AX18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AY18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AZ18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="BA18">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="BB18">
+        <f t="shared" ref="BB18:BE18" si="14">BB10</f>
+        <v>0.5</v>
+      </c>
+      <c r="BC18">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="BD18">
+        <f t="shared" si="14"/>
+        <v>0.5</v>
+      </c>
+      <c r="BE18">
+        <f t="shared" si="14"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -3367,8 +4787,68 @@
       <c r="AK19">
         <v>0</v>
       </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -3480,8 +4960,68 @@
       <c r="AK20">
         <v>0</v>
       </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -3593,8 +5133,68 @@
       <c r="AK21">
         <v>0</v>
       </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -3706,8 +5306,68 @@
       <c r="AK22">
         <v>0</v>
       </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -3819,8 +5479,68 @@
       <c r="AK23">
         <v>0</v>
       </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -3932,8 +5652,68 @@
       <c r="AK24">
         <v>0</v>
       </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:57" x14ac:dyDescent="0.75">
       <c r="A25" s="4" t="s">
         <v>40</v>
       </c>
@@ -4043,6 +5823,66 @@
         <v>0</v>
       </c>
       <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
         <v>0</v>
       </c>
     </row>
